--- a/jogos_2024-11-05.xlsx
+++ b/jogos_2024-11-05.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,19 +643,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.75</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>4.33</v>
+        <v>1.89</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="T2" t="n">
-        <v>2.63</v>
+        <v>3.32</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['12', '54']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>2.92</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.6</v>
+        <v>1.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.53</v>
+        <v>4.7</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45601.60416666666</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,19 +772,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>3.75</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.89</v>
+        <v>4.33</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>2.63</v>
       </c>
       <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.64</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['12', '54']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.02</v>
+        <v>1.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.92</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.28</v>
+        <v>2.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.7</v>
+        <v>1.53</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45601.60416666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.45</v>
+        <v>1.79</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.07</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['16', '33', '83', '88']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.44</v>
       </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['10', '30', '54', '72']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45601.61458333334</v>
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.79</v>
+        <v>3.45</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>2.07</v>
       </c>
       <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.25</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['10', '30', '54', '72']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AJ5" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['16', '33', '83', '88']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45601.61458333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.5</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>3.71</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.06</v>
+        <v>4.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['10', '11', '18', '70', '77']</t>
+          <t>['86', '90+8']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45601.69791666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45601.69791666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.9</v>
+        <v>2.28</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['12', '34']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['31', '35', '87', '90+5']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45601.69791666666</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -1596,31 +1596,31 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
         <v>1.67</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['12', '34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45601.69791666666</v>
@@ -1675,81 +1675,81 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
         <v>2</v>
@@ -1759,25 +1759,25 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['86', '90+8']</t>
+          <t>['31', '35', '87', '90+5']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45601.69791666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.35</v>
       </c>
-      <c r="X11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '11', '18', '70', '77']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45601.69791666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['38', '46', '49', '80']</t>
+          <t>['61', '63', '83', '90+2']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>2.23</v>
       </c>
       <c r="AI12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.63</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,16 +2062,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.2</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.25</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD13" t="n">
         <v>2.2</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['61', '63', '83', '90+2']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.14</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '46', '49', '80']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>2.09</v>
       </c>
       <c r="AH14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['12', '39', '73']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,55 +2475,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.17</v>
+        <v>1.56</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>1.62</v>
@@ -2533,25 +2533,25 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '39', '73']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,55 +2604,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>1.18</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.36</v>
       </c>
-      <c r="X17" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
         <v>1.91</v>
@@ -2662,25 +2662,25 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI17" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>15</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.5</v>
+        <v>2.63</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>6.4</v>
+        <v>4.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['35', '45+1', '72']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>2.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X19" t="n">
         <v>3.25</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.45</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['35', '45+1', '72']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45601.70833333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.36</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45601.70833333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="M27" t="n">
         <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['24', '37', '47', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['40', '66', '90+1']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45601.89583333334</v>
@@ -3997,23 +3997,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
@@ -4023,28 +4023,28 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.4</v>
       </c>
-      <c r="M28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N28" t="n">
-        <v>8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
         <v>2.75</v>
@@ -4056,32 +4056,32 @@
         <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AA28" t="n">
         <v>3.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['42', '90+3']</t>
+          <t>['9', '12', '71']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45601.89583333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['24', '37', '47', '52']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.44</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['9', '12', '71']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45601.89583333334</v>
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
         <v>3</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['42', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>4.33</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['40', '66', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45601.89583333334</v>
